--- a/beta_12wok/summary_odp_black_special_value_hq.xlsx
+++ b/beta_12wok/summary_odp_black_special_value_hq.xlsx
@@ -85,10 +85,10 @@
     <t>BALI BARAT</t>
   </si>
   <si>
-    <t>BALI TENGAH</t>
-  </si>
-  <si>
-    <t>KUPANG ROTE</t>
+    <t>BALI TENGAH 2</t>
+  </si>
+  <si>
+    <t>KUPANG ROTE - MALAKA TIMTIM BELU</t>
   </si>
   <si>
     <t>LOMBOK</t>

--- a/beta_12wok/summary_odp_black_special_value_hq.xlsx
+++ b/beta_12wok/summary_odp_black_special_value_hq.xlsx
@@ -85,10 +85,10 @@
     <t>BALI BARAT</t>
   </si>
   <si>
-    <t>BALI TENGAH 2</t>
-  </si>
-  <si>
-    <t>KUPANG ROTE - MALAKA TIMTIM BELU</t>
+    <t>BALI TENGAH</t>
+  </si>
+  <si>
+    <t>KUPANG ROTE</t>
   </si>
   <si>
     <t>LOMBOK</t>

--- a/beta_12wok/summary_odp_black_special_value_hq.xlsx
+++ b/beta_12wok/summary_odp_black_special_value_hq.xlsx
@@ -525,16 +525,16 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>26</v>
@@ -569,16 +569,16 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>9.73</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -613,16 +613,16 @@
         <v>2</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -657,16 +657,16 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>23</v>
@@ -701,16 +701,16 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -745,16 +745,16 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -789,16 +789,16 @@
         <v>2</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -833,16 +833,16 @@
         <v>29</v>
       </c>
       <c r="D9">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>23</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -921,16 +921,16 @@
         <v>2</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -965,16 +965,16 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -1009,16 +1009,16 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <v>15</v>
@@ -1053,16 +1053,16 @@
         <v>4</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="H14">
         <v>3</v>
@@ -1097,16 +1097,16 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="H15">
         <v>2</v>

--- a/beta_12wok/summary_odp_black_special_value_hq.xlsx
+++ b/beta_12wok/summary_odp_black_special_value_hq.xlsx
@@ -555,7 +555,7 @@
         <v>4.8</v>
       </c>
       <c r="N2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -599,7 +599,7 @@
         <v>9.1</v>
       </c>
       <c r="N3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -731,7 +731,7 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1127,7 +1127,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/beta_12wok/summary_odp_black_special_value_hq.xlsx
+++ b/beta_12wok/summary_odp_black_special_value_hq.xlsx
@@ -549,13 +549,13 @@
         <v>33.3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="N2">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -681,13 +681,13 @@
         <v>17.2</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -857,13 +857,13 @@
         <v>17.2</v>
       </c>
       <c r="L9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1033,13 +1033,13 @@
         <v>15.8</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:14">

--- a/beta_12wok/summary_odp_black_special_value_hq.xlsx
+++ b/beta_12wok/summary_odp_black_special_value_hq.xlsx
@@ -537,16 +537,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I2">
-        <v>61.9</v>
+        <v>59.5</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K2">
-        <v>33.3</v>
+        <v>35.7</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -669,16 +669,16 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5">
-        <v>79.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>17.2</v>
+        <v>20.7</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -845,16 +845,16 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I9">
-        <v>79.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>17.2</v>
+        <v>20.7</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -1021,16 +1021,16 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I13">
-        <v>78.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13">
-        <v>15.8</v>
+        <v>21.1</v>
       </c>
       <c r="L13">
         <v>0</v>

--- a/beta_12wok/summary_odp_black_special_value_hq.xlsx
+++ b/beta_12wok/summary_odp_black_special_value_hq.xlsx
@@ -537,16 +537,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I2">
-        <v>59.5</v>
+        <v>57.1</v>
       </c>
       <c r="J2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K2">
-        <v>35.7</v>
+        <v>38.1</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -555,7 +555,7 @@
         <v>2.4</v>
       </c>
       <c r="N2">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -581,16 +581,16 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>18.2</v>
+        <v>9.1</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K3">
-        <v>72.7</v>
+        <v>81.8</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -599,7 +599,7 @@
         <v>9.1</v>
       </c>
       <c r="N3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -713,16 +713,16 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -731,7 +731,7 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1109,16 +1109,16 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="L15">
         <v>1</v>
@@ -1127,7 +1127,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/beta_12wok/summary_odp_black_special_value_hq.xlsx
+++ b/beta_12wok/summary_odp_black_special_value_hq.xlsx
@@ -549,13 +549,13 @@
         <v>38.1</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="N2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -681,13 +681,13 @@
         <v>20.7</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -857,13 +857,13 @@
         <v>20.7</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1033,13 +1033,13 @@
         <v>21.1</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N13">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:14">
